--- a/test/fixtures/clean.xlsx
+++ b/test/fixtures/clean.xlsx
@@ -425,6 +425,7 @@
       </c>
       <c r="D2">
         <f>B2*C2</f>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -439,6 +440,7 @@
       </c>
       <c r="D3">
         <f>B3*C3</f>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -453,6 +455,7 @@
       </c>
       <c r="D4">
         <f>B4*C4</f>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
